--- a/Scholarship_and_Visa_Application_Tracker_2026.xlsx
+++ b/Scholarship_and_Visa_Application_Tracker_2026.xlsx
@@ -14,6 +14,7 @@
     <sheet name="Russia_Open_Doors" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Hungary_Stipendium" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Romania_Work_Visa" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="France_Campus_France" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -25,7 +26,40 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="516">
+  <si>
+    <t xml:space="preserve">France (EU)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campus France / Études en France (EEF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSc Computer Science / Cloud &amp; AI (Grenoble Alpes, Lille, Paris-Saclay)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOI Accepted (NO IELTS) + Eiffel Eligible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fall 2027 (Sept 2027)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EEF Cart Intake: Monitoring Daily | Closes: March 1–15, 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partial Exoneration (~€243/yr fee) + Eiffel Fellowship (€1,181/mo) + CROUS Housing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95% (Candidate ID: ET26-00453)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOSSIER COMPLETED (AWAITING CART UNLOCK) - REMINDER SET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOP PRIORITY (P1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check portal twice weekly for intake opening; submit 4 target programs (IDs 61801, 61800, 60987, 60589)</t>
+  </si>
   <si>
     <t xml:space="preserve">GLOBAL SCHOLARSHIP &amp; UNIVERSITY OPPORTUNITY TRACKER (2026–2027)</t>
   </si>
@@ -93,9 +127,6 @@
     <t xml:space="preserve">PREPARING MOI &amp; DOSSIER</t>
   </si>
   <si>
-    <t xml:space="preserve">TOP PRIORITY (P1)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Obtain MOI letter from St. Mary's Registrar; submit pre-enrollment</t>
   </si>
   <si>
@@ -108,9 +139,6 @@
     <t xml:space="preserve">MSc Computer Science (HIT, BIT, USTC)</t>
   </si>
   <si>
-    <t xml:space="preserve">Fall 2027 (Sept 2027)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Feb 15 – Mar 15, 2027</t>
   </si>
   <si>
@@ -270,6 +298,93 @@
     <t xml:space="preserve">NON-IELTS FULLY FUNDED UNIVERSITIES &amp; PROGRESS TRACKER (2026–2027)</t>
   </si>
   <si>
+    <t xml:space="preserve">France</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Université Grenoble Alpes (UGA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSc Informatique - MoSIG (M1) [Program ID: 61801]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exonération Partielle (Nominal Fee: €243/yr) + Eiffel Excellence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96% Tuition Waiver (Pay ~€243/yr) + CROUS Housing + €1,181/mo Eiffel Option</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOI Accepted (100% English Taught)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00 (Fuad: 3.20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fall 2027 (Starts Sept 2027)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EEF Cart Intake: Monitoring Daily | Closes March 1–15, 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOSSIER VALIDATED (EEF: ET26-00453) - Program Cart Pending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://etudesenfrance.diplomatie.gouv.fr/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">World top 100 CS faculty; €243/yr nominal tuition waiver; no IELTS required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSc Cloud Computing &amp; Data Infrastructures (M2) [Program ID: 61800]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exonération Partielle (Nominal Fee: €243/yr) + IdEx Grant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96% Tuition Waiver (Pay ~€243/yr) + CROUS Housing + Paid Lab Research Internship</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct specialization in Fuad's cloud/backend expertise; Grenoble high-tech hub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Université de Lille</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master Informatique - parcours Computer Sciences (M1) [Program ID: 60987]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exonération Partielle (Nominal Fee: €243/yr) + Bourse de Mobilité</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96% Tuition Waiver (Pay ~€243/yr) + CROUS Housing + Subsidies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Major French research university; full English track; low cost of living; high visa grant rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CentraleSupélec / Université Paris-Saclay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSc in Artificial Intelligence [Program ID: 60589]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campus France Eiffel Excellence Scholarship + University Merit Grant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100% Tuition Waiver + €1,181/mo Stipend + Return Flight + Priority CROUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20 (Fuad: 3.20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eiffel: Nov 2026 – Jan 2027 | EEF Cart Intake: Monitoring Daily</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOSSIER VALIDATED (EEF: ET26-00453) - Eiffel Nomination Track</t>
+  </si>
+  <si>
+    <t xml:space="preserve">France's #1 institution for AI and Mathematics; elite Grande École prestige</t>
+  </si>
+  <si>
     <t xml:space="preserve">All universities listed below accept an official English Medium of Instruction (MOI) Certificate from St. Mary's University in place of IELTS / TOEFL.</t>
   </si>
   <si>
@@ -462,9 +577,6 @@
     <t xml:space="preserve">75%</t>
   </si>
   <si>
-    <t xml:space="preserve">Fall 2027 (Starts Sept 2027)</t>
-  </si>
-  <si>
     <t xml:space="preserve">February 15, 2027 (Opens Dec 2026)</t>
   </si>
   <si>
@@ -1096,6 +1208,372 @@
   </si>
   <si>
     <t xml:space="preserve">Embassy interview in Addis Ababa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANCE: ÉTUDES EN FRANCE (CAMPUS FRANCE) CANDIDATE DOSSIER &amp; PROGRAM TRACKER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Candidate: Fuad Ahmed (TUBA FUAD AHMED) | EEF ID: ET26-00453 | Passport: E00340202 | Status: DOSSIER 100% COMPLETED | Intake: Fall 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Category / Milestone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target Degree / Item Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Program ID / Reference Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scholarship &amp; Funding Mechanism</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target Intake &amp; Timeline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Application Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Official Link / Portal Reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Action Required &amp; Scheduled Reminder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EEF Account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Candidate Official Identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ET26-00453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Espace Campus France Éthiopie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fall 2027 Cycle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTIVE &amp; VALIDATED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://etudesenfrance.diplomatie.gouv.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Credentials stored; official dossier number assigned for university admissions &amp; visa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identity Verification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUBA, FUAD AHMED (DOB: 16/02/1999)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passport: E00340202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valid through 15/04/2036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Official ICS Passport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UPLOADED &amp; VERIFIED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01_Master_Application_Dossier/passport.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full biometric passport verified and attached to EEF profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Higher Education (Cursus)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc in Computer Science (St. Mary's Univ.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPA: 3.20/4.00 (Grad. 2022)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equated to French Licence (Bac+3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fall 2018 – Aug 2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALL 3 PAGES UPLOADED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuad_Ahmed_BSc_Degree_Complete_3Pages.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Combined 3-page single PDF with Degree certificate and 2-page complete transcripts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secondary Education</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grade 12 National Exam &amp; Grade 10 EGSECE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Certificate: 377/700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equated to French Baccalauréat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Completed 2017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALL PAGES UPLOADED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuad_Ahmed_High_School_Certificates.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Combined certificate scan verified and attached in school record</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Academic Dossier Files</t>
+  </si>
+  <si>
+    <t xml:space="preserve">French Standard Academic CV &amp; 2-Page SOP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Version 2026-2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard French Master format</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Academic Year 2026–2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINALIZED &amp; ATTACHED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuad_Ahmed_CV_France_Academic.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aligned with European ECTS and French computer science master requirements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Language Proficiency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">English MOI &amp; French A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">St. Mary's MOI Letter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100% English Instruction Exemption</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fall 2027 Intake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXEMPT (NO IELTS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">St. Mary's MOI Certificate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Universities waive IELTS based on English Medium of Instruction; French A1 noted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target Program 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Université Grenoble Alpes - Master Informatique (MoSIG M1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Program ID: 61801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exonération Partielle (~€243/yr fee) + Eiffel Eligible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">READY TO SUBMIT IN CART</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EEF Catalog ID 61801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REMINDER: Add to cart as soon as intake opens; check twice weekly (Deadline: Mar 1–15, 2027)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target Program 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Université Grenoble Alpes - Cloud Computing &amp; Data Infra (M2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Program ID: 61800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exonération Partielle (~€243/yr fee) + IdEx Grant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EEF Catalog ID 61800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REMINDER: Add to cart as soon as intake opens; directly aligns with cloud engineering expertise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target Program 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Université de Lille - Master Informatique Computer Sciences (M1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Program ID: 60987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exonération Partielle (~€243/yr fee) + Subsidies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EEF Catalog ID 60987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REMINDER: Add to cart as soon as intake opens; top northern France tech cluster (Deadline: Mar 1–15, 2027)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target Program 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CentraleSupélec / Paris-Saclay - MSc in Artificial Intelligence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Program ID: 60589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campus France Eiffel Excellence (€1,181/mo + Tuition Waiver)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EEF Catalog ID 60589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REMINDER: Apply for Eiffel nomination via university coordinator (Deadline: Nov 2026 - Jan 2027)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calendar Reminder 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portal Cart Intake Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status: Out of Period Check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Central Ministry Administration Update</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every Monday &amp; Friday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTIVE REMINDER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REMINDER: Log in as ET26-00453 to check if intake window is opened by central ministry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calendar Reminder 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eiffel Excellence Scholarship Nomination Outreach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CentraleSupélec &amp; UGA International Relations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full scholarship (€1,181/mo + flights + tuition waiver)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nov 15, 2026 – Jan 10, 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCHEDULED OUTREACH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">campusfrance.org/en/eiffel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REMINDER: Email academic directors with French CV &amp; SOP for institutional Eiffel sponsorship</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calendar Reminder 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final Cart Submission &amp; EEF Application Fee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campus France Dossier Submission</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EEF Application Fee (~€50-€100)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deadline: March 1–15, 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCHEDULED MILESTONE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EEF Candidate Portal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REMINDER: Finalize 4 choices in cart with tailored motivation statements before March deadline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calendar Reminder 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campus France Ethiopia In-Person Interview</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alliance Éthio-Française Addis Ababa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Academic &amp; Study Project Validation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">March – April 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UPCOMING INTERVIEW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campus France Addis Ababa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REMINDER: Attend interview with hard copies of 3-page degree, transcripts, and Study Project</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calendar Reminder 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visa Application (VLS-TS Étudiant)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Embassy of France in Ethiopia / VFS Global</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schengen Long-Stay Student Visa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">May – July 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINAL STAGE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">france-visas.gouv.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REMINDER: Book VFS appointment immediately upon receiving Accord Préalable d'Inscription</t>
   </si>
 </sst>
 </file>
@@ -1124,27 +1602,6 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="14"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Inter;-apple-system"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="10"/>
-      <color rgb="FF94A3B8"/>
-      <name val="Inter;-apple-system"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10.5"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Inter;-apple-system"/>
       <family val="0"/>
     </font>
     <font>
@@ -1203,6 +1660,27 @@
       <family val="0"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Inter;-apple-system"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="10"/>
+      <color rgb="FF94A3B8"/>
+      <name val="Inter;-apple-system"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10.5"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Inter;-apple-system"/>
+      <family val="0"/>
+    </font>
+    <font>
       <i val="true"/>
       <sz val="10"/>
       <color rgb="FFD1FAE5"/>
@@ -1223,24 +1701,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF0F172A"/>
-        <bgColor rgb="FF1E293B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E293B"/>
-        <bgColor rgb="FF0F172A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E3A8A"/>
-        <bgColor rgb="FF334155"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1280,6 +1740,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF0F172A"/>
+        <bgColor rgb="FF1E293B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E293B"/>
+        <bgColor rgb="FF0F172A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E3A8A"/>
+        <bgColor rgb="FF334155"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF064E3B"/>
         <bgColor rgb="FF065F46"/>
       </patternFill>
@@ -1303,21 +1781,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="hair">
-        <color rgb="FF3B82F6"/>
-      </left>
-      <right style="hair">
-        <color rgb="FF3B82F6"/>
-      </right>
-      <top style="hair">
-        <color rgb="FF3B82F6"/>
-      </top>
-      <bottom style="hair">
-        <color rgb="FF3B82F6"/>
-      </bottom>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
@@ -1427,6 +1890,21 @@
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="hair">
+        <color rgb="FF3B82F6"/>
+      </left>
+      <right style="hair">
+        <color rgb="FF3B82F6"/>
+      </right>
+      <top style="hair">
+        <color rgb="FF3B82F6"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="FF3B82F6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="hair">
         <color rgb="FF059669"/>
       </left>
       <right style="hair">
@@ -1486,63 +1964,63 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="7" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="8" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="9" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="10" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="10" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="12" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="12" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="13" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="13" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1729,317 +2207,352 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultColWidth="9.92578125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="31.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="20.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="21.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="J1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="3" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="10" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="11" t="s">
         <v>21</v>
       </c>
       <c r="J5" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K5" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="7" t="s">
+      <c r="D6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="E6" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="F6" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="G6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="H6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="J6" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K6" s="5" t="s">
+      <c r="I6" s="7" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="J6" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="5" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="B7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="7" t="s">
+      <c r="C7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" s="5" t="s">
+      <c r="E7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="G7" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="H7" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="J7" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K7" s="5" t="s">
+      <c r="I7" s="6" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="J7" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="5" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="B8" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="7" t="s">
+      <c r="C8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="G8" s="5" t="s">
+      <c r="E8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="G8" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="H8" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="J8" s="9" t="s">
+      <c r="I8" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="J8" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="8" t="s">
+      <c r="G9" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="H9" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="I9" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="J9" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="J9" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="K9" s="5" t="s">
+      <c r="K9" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="G10" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="H10" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="I10" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I10" s="9" t="s">
+      <c r="J10" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="K10" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="J10" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="K10" s="5" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="B11" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="C11" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="D11" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="E11" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="F11" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="G11" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="H11" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="I11" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="I11" s="10" t="s">
+      <c r="J11" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="K11" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="J11" s="5" t="s">
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="B12" s="2" t="s">
         <v>79</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -2058,12 +2571,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr defaultColWidth="9.92578125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="31.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -2077,590 +2590,742 @@
       <c r="K1" s="12"/>
       <c r="L1" s="12"/>
     </row>
-    <row r="2" customFormat="false" ht="20.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-    </row>
-    <row r="4" customFormat="false" ht="21.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="F4" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="H4" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="I4" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="J4" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="K4" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="L4" s="14" t="s">
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="B2" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D2" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E2" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F2" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="5" t="s">
+      <c r="G2" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H2" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+    </row>
+    <row r="8" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="H8" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I8" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="L8" s="14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="H14" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="J5" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="J6" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="J7" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="L9" s="5" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="E10" s="5" t="s">
+      <c r="I14" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="F10" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="E11" s="5" t="s">
+      <c r="H19" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="F11" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="L11" s="5" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="K12" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="L12" s="5" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="4" t="s">
+      <c r="H20" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="J13" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="K13" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="L13" s="5" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="K14" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="L14" s="5" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="K15" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="L15" s="5" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="J16" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="K16" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="L16" s="5" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="J17" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="K17" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="L17" s="5" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+      <c r="D21" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="J18" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="K18" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="L18" s="5" t="s">
-        <v>208</v>
+      <c r="H22" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -2682,325 +3347,325 @@
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultColWidth="9.92578125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="31.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="20.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="20.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>211</v>
+        <v>248</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>212</v>
+        <v>249</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>213</v>
+        <v>250</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>214</v>
+        <v>251</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>215</v>
+        <v>252</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>216</v>
+        <v>253</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>217</v>
+        <v>254</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>218</v>
+        <v>255</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>219</v>
+        <v>256</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>220</v>
+        <v>257</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>221</v>
+        <v>258</v>
       </c>
       <c r="M4" s="15" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="M6" s="5" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="M7" s="5" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="L9" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="M9" s="5" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="C10" s="4" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="E10" s="5" t="s">
+      <c r="B5" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="D5" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="G10" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="M10" s="5" t="s">
+      <c r="E5" s="2" t="s">
         <v>263</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -3022,164 +3687,164 @@
   <dimension ref="A1:G9"/>
   <sheetFormatPr defaultColWidth="9.92578125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="31.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="20.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="20.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>266</v>
+        <v>303</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>267</v>
+        <v>304</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>268</v>
+        <v>305</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>269</v>
+        <v>306</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>271</v>
+        <v>308</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>300</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>302</v>
+        <v>309</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -3201,132 +3866,132 @@
   <dimension ref="A1:H7"/>
   <sheetFormatPr defaultColWidth="9.92578125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="31.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="20.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="15" t="s">
         <v>304</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="20.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="15" t="s">
-        <v>305</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>267</v>
-      </c>
       <c r="E4" s="15" t="s">
-        <v>218</v>
+        <v>255</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>306</v>
+        <v>343</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>307</v>
+        <v>344</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="8" t="s">
         <v>309</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>311</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>325</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>328</v>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -3348,118 +4013,118 @@
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultColWidth="9.92578125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="31.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="20.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="20.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>331</v>
+        <v>368</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>332</v>
+        <v>369</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>333</v>
+        <v>370</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>335</v>
+        <v>372</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>218</v>
+        <v>255</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>341</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>348</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>356</v>
+        <v>309</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -3471,4 +4136,463 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr defaultColWidth="9.92578125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="10" t="s">
+        <v>395</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="15" t="s">
+        <v>396</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>397</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>398</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>399</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>400</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>401</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>402</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>441</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>482</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>497</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>504</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>505</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>512</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>513</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>515</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="0.886111111111111" bottom="0.886111111111111" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>